--- a/tests/fixtures/sample.xlsx
+++ b/tests/fixtures/sample.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,30 @@
       </c>
       <c r="C3" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Required</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>*</t>
+          </r>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -471,9 +495,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B2"/>
+  <dimension ref="B1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
